--- a/data/2026/37-timis/155243-timisoara/budget_file.xlsx
+++ b/data/2026/37-timis/155243-timisoara/budget_file.xlsx
@@ -19327,7 +19327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19373,12 +19373,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19386,54 +19386,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>05.00.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 05.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19442,41 +19432,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -19486,7 +19471,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total: parent 330.233.900,00 != sum(children) 428.734.180,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19502,66 +19487,66 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>18.00.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>code 18.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05.00.01</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>code 05.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -19577,11 +19562,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -19591,7 +19576,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.02 total: parent 330.233.900,00 != sum(children) 428.734.180,00 (1 children)</t>
+          <t>30.02 total: parent 27.979.510,00 != sum(children) 80.310.510,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19611,12 +19596,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.00.01</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>code 18.00.01 (revenue) not in nomenclator</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -19632,23 +19617,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -19657,16 +19642,21 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>42.02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>42.02 total: parent 621.042.190,00 != sum(children) 709.270.290,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19682,11 +19672,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -19696,39 +19686,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30.02 total: parent 27.979.510,00 != sum(children) 80.310.510,00 (1 children)</t>
+          <t>51.02 total: parent 125.558.980,00 != sum(children) 13.483.880,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -19737,16 +19727,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -19762,11 +19752,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -19776,19 +19766,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.02 total: parent 621.042.190,00 != sum(children) 709.270.290,00 (1 children)</t>
+          <t>61.02 total: parent 42.947.100,00 != sum(children) 3.727.090,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -19796,42 +19786,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.02 total: parent 125.558.980,00 != sum(children) 13.483.880,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>65.02 total: parent 393.115.780,00 != sum(children) 23.435.080,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -19847,7 +19837,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -19872,11 +19862,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -19886,7 +19876,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.02 total: parent 42.947.100,00 != sum(children) 3.727.090,00 (1 children)</t>
+          <t>66.02 total: parent 133.675.220,00 != sum(children) 6.443.200,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -19902,7 +19892,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -19931,7 +19921,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -19941,7 +19931,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.02 total: parent 393.115.780,00 != sum(children) 23.435.080,00 (2 children)</t>
+          <t>67.02 total: parent 393.709.290,00 != sum(children) 126.309.440,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19957,7 +19947,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -19982,11 +19972,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -19996,7 +19986,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>66.02 total: parent 133.675.220,00 != sum(children) 6.443.200,00 (2 children)</t>
+          <t>68.02 total: parent 214.705.450,00 != sum(children) 1.656.300,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20012,7 +20002,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -20037,11 +20027,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -20051,7 +20041,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>67.02 total: parent 393.709.290,00 != sum(children) 126.309.440,00 (1 children)</t>
+          <t>70.02 total: parent 256.404.670,00 != sum(children) 95.354.720,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20092,11 +20082,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -20106,7 +20096,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>68.02 total: parent 214.705.450,00 != sum(children) 1.656.300,00 (1 children)</t>
+          <t>74.02 total: parent 113.687.220,00 != sum(children) 742.300,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20112,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -20147,11 +20137,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -20161,7 +20151,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.02 total: parent 256.404.670,00 != sum(children) 95.354.720,00 (2 children)</t>
+          <t>81.02 total: parent 276.190.360,00 != sum(children) 59.690.360,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20177,7 +20167,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -20206,7 +20196,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -20216,7 +20206,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>74.02 total: parent 113.687.220,00 != sum(children) 742.300,00 (1 children)</t>
+          <t>84.02 total: parent 791.795.170,00 != sum(children) 117.066.620,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20257,11 +20247,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -20271,39 +20261,39 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>81.02 total: parent 276.190.360,00 != sum(children) 59.690.360,00 (1 children)</t>
+          <t>99.02 total: parent 95.888.040,00 != sum(children) 397.434.750,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -20312,21 +20302,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>05.00.01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>84.02 total: parent 791.795.170,00 != sum(children) 117.066.620,00 (1 children)</t>
+          <t>code 05.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -20336,59 +20321,54 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>01</t>
+        <v>8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>unparseable cell '428.734.180 330.233.900' in column total</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>99.02 total: parent 95.888.040,00 != sum(children) 397.434.750,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -20397,48 +20377,53 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>30.02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>30.02 total: parent 27.979.510,00 != sum(children) -256.939.480,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05.00.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>code 05.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -20447,7 +20432,12 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -20456,129 +20446,124 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>unparseable cell '428.734.180 330.233.900' in column total</t>
+          <t>70.02 total: parent 101.321.240,00 != sum(children) 50.474.240,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>99.02 total: parent 0,00 != sum(children) 50.474.240,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>30.02 total: parent 27.979.510,00 != sum(children) -256.939.480,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.02 total: parent 101.321.240,00 != sum(children) 50.474.240,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -20586,24 +20571,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>99.02 total: parent 0,00 != sum(children) 50.474.240,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20616,44 +20596,44 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -20662,16 +20642,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -20687,16 +20667,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -20712,16 +20692,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -20741,19 +20721,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -20766,12 +20746,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -20787,16 +20767,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>64.02</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -20812,16 +20792,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -20837,23 +20817,23 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -20862,16 +20842,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -20891,12 +20871,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>64.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20896,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -20941,12 +20921,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -20966,12 +20946,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -20991,12 +20971,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -21012,16 +20992,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -21037,16 +21017,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -21062,16 +21042,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -21087,11 +21067,11 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -21116,12 +21096,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -21141,12 +21121,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -21166,12 +21146,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -21187,16 +21167,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -21212,16 +21192,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -21237,16 +21217,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -21262,16 +21242,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -21291,110 +21271,10 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
-        <is>
-          <t>duplicate of p7 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>17</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>81.02</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>duplicate of p7 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>17</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>17</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>duplicate of p7 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>17</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
         <is>
           <t>duplicate of p3 with different values</t>
         </is>
@@ -21411,7 +21291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21433,7 +21313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -21443,60 +21323,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>340</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>269</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.09999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>e69fe8c0cbcc1ff2d59fe96c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>b254e8d7de2abc3d9ed143e2363e7b96cc80bcc13b8f40eb2996a1b68a77e85e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-17, 644 linii</t>
         </is>
